--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_detection/lang_detection__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_detection/lang_detection__ui__part_0001.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Discord thường hoạt động trong các khu mỏ và vùng núi, kích thước nhỏ, mức độ nguy hiểm tương đối thấp.</t>
+          <t>Tacet Discord thường hoạt động trong các khu mỏ và vùng núi, kích thước nhỏ, mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Resinacrustidum lapis", thuộc loài Resinacrustidum. Loại Discord này thường hoạt động theo đàn trong các khu mỏ và vùng núi cùng với các Fission Junrock khác, mức độ nguy hiểm tương đối thấp.</t>
+          <t>Tên khoa học "Resinacrustidum lapis", thuộc loài Resinacrustidum. Tacet Discord này thường hoạt động theo bầy trong các khu mỏ và vùng núi, cùng với các Fission Junrock khác, cấp độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Một loài Discord Tacet kích thước nhỏ thuộc chi Resinacrustidum, thường hoạt động theo bầy. Chủ yếu xuất hiện ở khu vực có nhiều khối đá. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Loài Tacet Discord nhỏ thuộc giống Resinacrustidum, thường hoạt động theo bầy đàn. Chủ yếu xuất hiện ở khu vực có nhiều khối đá. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Resinacrustidum lapis", thuộc loài Resinacrustidum. Loại Discord này thường hoạt động cùng với Vanguard Junrocks, mức độ nguy hiểm tương đối thấp.</t>
+          <t>Tên khoa học "Resinacrustidum lapis", thuộc loài Resinacrustidum. Tacet Discord này thường hoạt động cùng với các Vanguard Junrock, cấp độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Impulse Predator</t>
+          <t>Thú Dữ Dội</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Discord có ngoại hình giống con người, sở hữu chi trên chuyên biệt có thể sử dụng năng lượng dẫn điện để tấn công tầm xa. Theo lời nhân chứng, nó khá nguy hiểm.</t>
+          <t>Tacet Discord có hình dạng giống con người, sở hữu chi trên chuyên biệt có thể sử dụng năng lượng dẫn điện để tấn công tầm xa. Theo lời nhân chứng, nó khá nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Fusion Warrior</t>
+          <t>Chiến Binh Fusion</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Discord này có hình dạng giống người, phân bố rộng rãi. Các đòn tấn công chủ yếu ở tầm gần và rất nguy hiểm.</t>
+          <t>Hình dạng của Tacet Discord này giống hình người, phân bố rộng rãi. Các đòn tấn công chủ yếu ở tầm gần và rất nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Devorsonidum fusio", thuộc chi Devorsonidum. Hai chi trên đối xứng giống như giáo dài và ngắn, có thể tấn công bằng cách đâm và chém. Mức độ nguy hiểm trung bình.</t>
+          <t>Tên nhị thức "Devorsonidum fusio", thuộc chi Devorsonidum. Hai chi trước có hình dạng giống giáo dài và ngắn, có thể tấn công bằng cách đâm và chém. Mức độ nguy hiểm trung bình.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Rupture Warrior</t>
+          <t>Chiến Binh Đứt Gãy</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Một Discord hình người có phạm vi phân bố rộng, chủ yếu tấn công tầm gần. Có chi trên đặc trưng một bên, tiềm ẩn một số rủi ro.</t>
+          <t>Một Tacet Discord hình người phân bố rộng rãi, chủ yếu tấn công ở cự ly gần. Có chi trên đặc biệt lệch lạc, mang một số rủi ro.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Theo lời nhân chứng, các TD hình người xuất hiện rộng rãi có cánh tay chuyên dụng, tấn công chủ yếu ở cự ly gần và rất nguy hiểm.</t>
+          <t>Tổ Tacet hình người phổ biến, theo lời nhân chứng, có cánh tay chuyên biệt, tấn công chủ yếu ở cự ly gần và rất nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Devorsonidum spectrum", một thành viên của chi Devorsonidum.</t>
+          <t>Tên nhị thức "Devorsonidum spectrum", thuộc chi Devorsonidum.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Một Discord nhỏ phổ biến có thể giải phóng một lượng nhỏ năng lượng Havoc để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Một Tacet Discord nhỏ phổ biến, có thể giải phóng một lượng nhỏ năng lượng Havoc để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Một Discord nhỏ thông thường có thể giải phóng một lượng nhỏ năng lượng Aero để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Một Tacet Discord nhỏ phổ biến, có thể giải phóng một lượng nhỏ năng lượng Aero để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Một Discord kích cỡ nhỏ thông thường, có thể giải phóng một lượng nhỏ năng lượng Fusion để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Một Tacet Discord kích cỡ nhỏ phổ biến, có thể giải phóng một lượng nhỏ năng lượng Fusion để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Một Discord nhỏ thông thường, có thể giải phóng một lượng nhỏ năng lượng Spectra để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Một Tacet Discord nhỏ phổ biến, có thể giải phóng một lượng nhỏ năng lượng Spectro để tấn công. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Tên khoa học là "Strepoplasmidum spectrum", thuộc chi Strepoplasmidum. Được đặt tên như vậy do thiếu trí thông minh và hành vi logic đơn giản.</t>
+          <t>Được khoa học đặt tên là "Strepoplasmidum spectrum", thuộc chi Strepoplasmidum. Loài này có tên gọi như vậy do thiếu trí thông minh và hành vi logic đơn giản.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Pneuma Predator</t>
+          <t>Thú Dữ Pneuma</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Ngoại hình của TD này giống một thợ săn đội mũ bowler, xuất hiện khắp Tacet Fields, với đòn tấn công tầm xa đặc biệt và mức độ nguy hiểm nhất định.</t>
+          <t>Hình dạng của TD này giống một thợ săn đội mũ bowler, xuất hiện ở khắp các Tổ Tacet, sở hữu đòn tấn công tầm xa đặc biệt và có mức độ nguy hiểm nhất định.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Glacio Predator</t>
+          <t>Thú Dữ Glacio</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Một dạng TD hình người phổ biến được tìm thấy ở các Tacet Fields trên khắp thế giới. Theo lời nhân chứng, nó giống một thợ săn khoác áo choàng và có thể sử dụng năng lượng Glacio để tấn công tầm xa. Mức độ nguy hiểm trung bình.</t>
+          <t>Loài Tacet Discord hình người phổ biến trong các Tổ Tacet trên toàn thế giới. Theo lời kể của nhân chứng, nó giống một thợ săn khoác áo choàng và có thể sử dụng năng lượng Glacio để tấn công tầm xa. Mức độ nguy hiểm trung bình.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Spectra Prism</t>
+          <t>Lăng Kính Phổ</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Theo báo cáo quan sát, TD này thường xuất hiện trong hệ thống mạch Tacetite và có thể gây Spectro DMG.</t>
+          <t>Theo báo cáo quan sát, Tacet Discord này thường xuất hiện trong hệ thống mạch Tổ Tacet và có thể gây sát thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Resinacrustidum convenire", thuộc chi Resinacrustidum. Một trong nhiều Tacet Discord cấp độ nguy hiểm thấp được tìm thấy rộng rãi trên thế giới.</t>
+          <t>Tên khoa học "Resinacrustidum convenire", một thành viên của chi Resinacrustidum. Đây là một trong nhiều Tacet Discord cấp độ nguy hiểm thấp, phân bố rộng rãi trên toàn thế giới.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Theo báo cáo trinh sát, TD này thường xuất hiện trong hệ thống mạch Tacetite và có thể gây Glacio DMG.</t>
+          <t>Theo báo cáo quan sát, Tacet Discord này thường xuất hiện trong hệ thống mạch Tổ Tacet và có thể gây sát thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Rupture Prism</t>
+          <t>Lăng Kính Đột Phá</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Theo báo cáo trinh sát, TD này thường xuất hiện trong hệ thống mạch Tacetite và có thể gây Havoc DMG.</t>
+          <t>Theo báo cáo quan sát, Tacet Discord này thường xuất hiện trong hệ thống mạch Tổ Tacet và có thể gây sát thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Theo báo cáo quan sát, TD này thường xuất hiện trong hệ thống mạch Tacetite và có thể gây Fusion DMG.</t>
+          <t>Theo báo cáo quan sát, Tacet Discord này thường xuất hiện trong hệ thống mạch Tổ Tacet và có thể gây sát thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Chasm Guardian</t>
+          <t>Người Bảo Vệ Vực Sâu</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Loại TD này xuất hiện ở nhiều khu vực, có đặc điểm chi trên một bên tương tự như con người dùng một tay nâng khiên, rất nguy hiểm</t>
+          <t>Loại Tacet Discord này xuất hiện ở nhiều khu vực, có đặc điểm bất thường ở chi trên một bên, giống như con người giơ khiên một tay, và rất nguy hiểm</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Tên khoa học "Devorsonidum ruptura", một loài thuộc chi Devorsonidum.</t>
+          <t>Tên nhị thức "Devorsonidum ruptura", thuộc chi Devorsonidum.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Stonewall Bracer</t>
+          <t>Băng Tay Đá Tảng</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Thường thấy ở đồi núi và các địa điểm có dấu vết hoạt động của con người, phân bố rộng rãi, có mức độ nguy hiểm nhất định.</t>
+          <t>Thường xuất hiện ở các ngọn đồi núi và những nơi có Tổ Tacet giống con người, phân bố rộng rãi, mức độ nguy hiểm nhất định.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Tên khoa học "Resinacrustidum lapis", thuộc chi Resinacrustidum.</t>
+          <t>Tên khoa học "Resinacrustidum lapis", một thành viên của chi Resinacrustidum.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Flute Instrumentalist</t>
+          <t>Nghệ Nhân Sáo</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>TD dạng người, phân bố rộng và xuất hiện ở nhiều khu vực. Theo lời nhân chứng, đòn tấn công giống như con người chơi nhạc cụ hơi và khá nguy hiểm.</t>
+          <t>Tổ Tacet dạng người, phân bố rộng và xuất hiện ở nhiều khu vực. Theo lời kể của nhân chứng, cách tấn công của chúng giống như con người chơi các nhạc cụ hơi và khá nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Devorsonidum impulsio", một thành viên của chi Devorsonidum.</t>
+          <t>Tên nhị thức "Devorsonidum impulsio", thuộc chi Devorsonidum.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Tambourine Instrumentalist</t>
+          <t>Nghệ Sĩ Trống Lắc</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Các TD loại này phân bố rộng rãi và có thể nhìn thấy ở nhiều khu vực. Theo báo cáo, chúng có khả năng tác động đến hành động của đối thủ thông qua các đòn tấn công đặc biệt và khá nguy hiểm.</t>
+          <t>Những Tổ Tacet này phân bố rộng và xuất hiện ở nhiều khu vực. Các báo cáo quan sát cho thấy chúng có khả năng tác động đến hành động của đối thủ thông qua các đòn tấn công đặc biệt và khá nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tên khoa học "Devorsonidum ruptura", một loài thuộc chi Devorsonidum.</t>
+          <t>Tên nhị thức "Devorsonidum ruptura", thuộc chi Devorsonidum.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Sinh vật đột biến thủy sinh cỡ nhỏ, thường xuất hiện trong mạng lưới nước ngọt, có thói quen lén lút tiếp cận con mồi và ít nguy hiểm hơn.</t>
+          <t>Sinh Vật Đột Biến thủy sinh nhỏ, chủ yếu sống trong các mạng lưới nước ngọt, có thói quen lén lút tiếp cận con mồi, mức độ nguy hiểm thấp.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Tetraodon lateo", một Sinh Vật Đột Biến thuộc chi Tetraodon.</t>
+          <t>Tên khoa học "Tetraodon lateo", một Sinh Vật Đột Biến thuộc chi Tetraodon.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Sinh vật đột biến lớn đặc hữu của Huanglong, thường xuất hiện ở vùng lãnh thổ Huanglong giữa các vùng đầm lầy và hồ nước. Desorock Highland cũng có dấu vết của chúng, hung hăng và ý thức lãnh thổ rất mạnh, có mức độ nguy hiểm nhất định.</t>
+          <t>Sinh Vật Đột Biến Cỡ Lớn đặc hữu của Huanglong, thường xuất hiện ở vùng đất ngập nước và hồ nước thuộc lãnh thổ Huanglong. Desorock Highlands cũng có dấu vết của chúng, hung hăng và ý thức lãnh thổ rất mạnh, có mức độ nguy hiểm nhất định.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Tên khoa học ba phần "Ardea purpurea bipenna", một phân loài của Ardea purpurea chỉ có ở Huanglong.</t>
+          <t>Tên ba phần "Ardea purpurea bipenna", một phân loài của Ardea purpurea chỉ tìm thấy duy nhất ở Huanglong.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Một trong những loài chim lội lớn đặc hữu của Huanglong. Bản tính hung dữ, thường xuất hiện ở vùng nước Huanglong và Desorock Highland, có mức độ nguy hiểm nhất định.</t>
+          <t>Một trong những loài chim lội lớn đặc hữu của Huanglong. Bản tính hung dữ, thường xuất hiện ở vùng nước Huanglong và Desorock Highlands, có thể gây nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Tên khoa học ba phần "Ardea purpurea bipenna", một phân loài của Ardea purpurea chỉ có ở Huanglong.</t>
+          <t>Tên ba phần "Ardea purpurea bipenna", một phân loài của Ardea purpurea chỉ tìm thấy duy nhất ở Huanglong.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Thường thấy ở các vùng lãnh thổ thuộc Huanglong, các báo cáo hiện có cho biết nó chỉ xuất hiện vào ban ngày. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Thường được tìm thấy trong lãnh thổ Huanglong, các báo cáo hiện tại cho thấy nó chỉ xuất hiện vào ban ngày. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Tên khoa học "Acanthacorydalis squapenna", thuộc chi Resinacrustidum. Thường xuất hiện ở ven nước tại các khu vực ấm áp và ẩm ướt trên khắp Huanglong. Dù hơi hung dữ, chúng dễ bị săn bắt bởi Thằn Lằn Địa Ẩn và các loài khác, không quá nguy hiểm. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Tên nhị thức "Acanthacorydalis squapenna", thuộc chi Resinacrustidum. Thường xuất hiện ở các khu vực ven nước tại những vùng ấm áp và ẩm ướt trên khắp Huanglong. Dù hơi hung dữ, chúng lại dễ dàng trở thành con mồi của Geohide Saurian và các loài khác, nên không quá nguy hiểm. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Sabyr Boar</t>
+          <t>Lợn Rừng Sabyr</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Sinh Vật Biến Dị cỡ trung, tính khí hung dữ. Sống trên cạn, thường đi theo đàn, di chuyển và tấn công bằng cách lao tới, phân bố rộng. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Một Sinh Vật Đột Biến cỡ trung với tính khí hung dữ. Sống trên cạn, thường đi theo đàn, giỏi chạy và lao nhanh, phân bố rộng rãi. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Babyrousa fractden", một Mutant Organism thuộc chi Babyrousa. Là một Mutant Organism ăn tạp phổ biến khắp nơi. Mặc dù khẩu phần ăn chủ yếu có nguồn gốc thực vật, nhưng tính khí của nó không giống các loài ăn cỏ thông thường.</t>
+          <t>Tên nhị thức "Babyrousa fractden", một Sinh Vật Đột Biến thuộc chi Babyrousa. Là loài ăn tạp phổ biến khắp nơi. Dù chủ yếu ăn thực vật, nhưng tính khí của chúng không hề giống các loài ăn cỏ thông thường.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Sinh Vật Đột Biến nhỏ giống lợn thường thấy ở Huanglong, dễ tìm thấy ở những khu vực ấm áp vào ban ngày. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Sinh Vật Đột Biến giống lợn nhỏ phổ biến ở Huanglong, thường xuất hiện ở những khu vực ấm áp vào ban ngày. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Myospalax actinoaftia", một Mutant Organism thuộc chi Myospalax. Một loài gặm nhấm đột biến nhỏ phổ biến, thường thấy ở đồng cỏ hoặc rừng ôn đới và vùng núi.</t>
+          <t>Tên khoa học "Myospalax actinoaftia", một Sinh Vật Đột Biến thuộc chi Myospalax. Đây là loài gặm nhấm đột biến nhỏ phổ biến, thường xuất hiện ở đồng cỏ, rừng ôn đới và vùng núi.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Geohide Saurian Minor</t>
+          <t>Thằn Lằn Địa Ẩn Hạng Nhỏ</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Thường thấy dưới dạng bò sát non ở Desorock Highland. Theo nhân chứng, chúng thường đi theo cá thể trưởng thành và săn mồi theo đàn, rất nguy hiểm.</t>
+          <t>Thường thấy dưới dạng bò sát non ở Desorock Highlands. Theo lời nhân chứng, chúng thường đi theo cá thể trưởng thành và săn mồi theo đàn, rất nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Aigialosauridae lapis", một Sinh Vật Đột Biến thuộc chi Aigialosauridae. Loài thằn lằn này không có tập tính chăm sóc con non, do đó những con non mới nở chỉ có thể sống sót bằng cách bắt chước hành vi săn mồi của con trưởng thành, nhặt thức ăn thừa và nếu cần, sử dụng những con non khác làm mục tiêu săn mồi.</t>
+          <t>Tên nhị thức "Aigialosauridae lapis", một Sinh Vật Đột Biến thuộc chi Aigialosauridae. Loài thằn lằn này không có tập tính chăm sóc con non, vì vậy những con mới nở chỉ có thể sống sót bằng cách bắt chước hành vi săn mồi của con trưởng thành, ăn xác thối của con mồi và nếu cần, sử dụng những con non khác làm mục tiêu tập săn.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Sinh Vật Đột Biến thường xuất hiện ở Desorock Highland. Theo lời kể, đây là loài bò sát lớn, di chuyển nhanh và nguy hiểm hơn.</t>
+          <t>Sinh Vật Đột Biến này chủ yếu xuất hiện ở Desorock Highlands. Theo lời kể của nhân chứng, nó là một loài bò sát lớn, di chuyển nhanh và nguy hiểm hơn.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Aigialosauridae lapis", một Sinh vật đột biến thuộc chi Aigialosauridae.</t>
+          <t>Tên nhị thức "Aigialosauridae lapis", một Sinh Vật Đột Biến thuộc chi Aigialosauridae.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Roseshroom (Immature)</t>
+          <t>Nấm Hồng (Chưa Trưởng Thành)</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Loài thực vật đột biến giai đoạn trưởng thành, phân bố rộng rãi trên toàn cầu, ưa thích khu vực ẩm ướt có nhiều Tacetite. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Thực vật đột biến giai đoạn trưởng thành, phân bố rộng khắp thế giới, ưa thích khu vực ẩm ướt có nhiều Tacetite. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Agaricus mimetikos", một Sinh Vật Đột Biến thuộc chi Agaricus. Ở giai đoạn chưa trưởng thành, Roseshroom chưa có khả năng hấp thụ chất dinh dưỡng từ Tacetite, do đó cần thu thập chất dinh dưỡng từ các Roseshroom trưởng thành gần đó để sinh tồn.</t>
+          <t>Tên nhị thức "Agaricus mimetikos", một Sinh Vật Đột Biến thuộc chi Agaricus. Ở giai đoạn chưa trưởng thành, Roseshroom chưa có khả năng hấp thụ dưỡng chất từ Tacetite, do đó cần thu thập chất dinh dưỡng từ những cây Roseshroom trưởng thành gần đó để sinh tồn.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Roseshroom (Mature)</t>
+          <t>Nấm Hồng (Trưởng Thành)</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Thực vật đột biến phân bố rộng, chủ yếu xuất hiện ở khu vực có nhiều Tacetite, ít nguy hiểm hơn.</t>
+          <t>Thực vật đột biến phân bố rộng, chủ yếu xuất hiện ở khu vực có nhiều Tacetite, ít nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Tên nhị thức "Agaricus mimicus". Ưa bóng râm và độ ẩm, thường mọc thành nhóm hai hoặc ba ở các hang động phía tây giàu Tacetite.</t>
+          <t>Tên nhị thức "Agaricus mimicus". Ưa bóng râm và độ ẩm, thường tụ tập thành nhóm hai hoặc ba cá thể trong các hang động phía tây giàu Tacetite.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Rupture Dreadmane Major</t>
+          <t>Dreadmane Major Đột Phá</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Một loài chó phân bố rộng rãi với nhiều phân loài. Phân loài này dường như đã tiến hóa đặc biệt cho thuộc tính Havoc. Có mức độ nguy hiểm nhất định.</t>
+          <t>Một loài chó phân bố rộng rãi với nhiều phân loài. Phân loài này dường như đã tiến hóa đặc biệt để thích nghi với thuộc tính Havoc. Có mức độ nguy hiểm nhất định.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Tên khoa học ba phần "Chrysocyon brachyurus terreo". Dreadmane trưởng thành có kích thước lớn hơn, di chuyển và hoạt động về đêm, sống theo bầy đàn, có tính xã hội cao và hung dữ.</t>
+          <t>Tên ba phần "Chrysocyon brachyurus terreo". Dreadmane trưởng thành có kích thước lớn hơn, di chuyển và hoạt động về đêm, sống theo bầy đàn, với đặc tính xã hội mạnh mẽ và hung hãn.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Một loài chó nhỏ phân bố rộng rãi với nhiều phân loài, thường đi theo đàn con. Phân loài này dường như đã tiến hóa đặc tính Fusion và ít nguy hiểm hơn.</t>
+          <t>Một loài chó con phân bố rộng rãi với nhiều phân loài, thường đi theo đàn con trưởng thành. Phân loài này dường như đã tiến hóa đặc tính chuyên biệt cho thuộc tính Fusion và ít nguy hiểm hơn.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Tên khoa học "Chrysocyon brachyurus terreo", một Sinh Vật Đột Biến thuộc phân loài Chrysocyon brachyurus.</t>
+          <t>Tên ba phần "Chrysocyon brachyurus terreo", một Sinh Vật Đột Biến thuộc phân loài Chrysocyon brachyurus.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Dân Lưu Đày</t>
+          <t>Dân Lưu Đày Thường</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Những cá nhân nguy hiểm lang thang nơi hoang dã ở nhiều quốc gia, thường hoạt động theo nhóm, xuất hiện theo nhóm, dễ đối phó nếu đơn lẻ. Mức độ nguy hiểm tương đối thấp.</t>
+          <t>Những cá nhân nguy hiểm lang thang ở vùng hoang dã của các quốc gia, thường hoạt động theo nhóm và xuất hiện theo nhóm, dễ đối phó nếu đơn lẻ. Mức độ nguy hiểm tương đối thấp.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>"Lưu Đày" là cái tên mang tội ác không thể tha thứ. Họ không được phép vào thị trấn, đành lang thang nơi hoang dã. Dù hầu hết Lưu Đày chỉ phải trả giá cho lỗi lầm trong quá khứ, nhưng do không phải phiên tòa nào ở các quốc gia cũng "công bằng", nên cũng có không ít người bị lưu đày oan và đang nổi dậy với lòng căm phẫn.</t>
+          <t>Cái tên "Kẻ Lưu Đày" mang theo trọng tội không thể tha thứ. Họ không được phép vào các thị trấn, đành lang thang nơi hoang dã. Dù phần lớn Kẻ Lưu Đày chỉ phải trả giá cho những lỗi lầm trong quá khứ, nhưng xét rằng không phải phiên tòa nào ở các quốc gia cũng "công bằng", vẫn có không ít người bị lưu đày oan uổng và đang nổi dậy với lòng căm phẫn.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Lãnh Đạo Lưu Đày</t>
+          <t>Thủ Lĩnh Lưu Đày</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Thủ lĩnh của nhóm lưu dân, thường xuất hiện tại Khu cắm trại Lưu đày trên khắp thế giới, có nhiều kinh nghiệm chiến đấu và kỹ năng hơn so với Lưu dân thông thường, khá nguy hiểm.</t>
+          <t>Kẻ cầm đầu bọn lưu vong, thường xuất hiện tại các Bãi tập trung Lưu vong trên khắp thế giới, có kinh nghiệm và kỹ năng chiến đấu vượt trội so với Lưu vong thông thường, và khá nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Các Thủ Lĩnh Lưu Đày hầu hết đều là Resonators. Ví dụ, ở khu vực Huanglong, các Thủ Lĩnh Lưu Đày thường là những người bị trục xuất khỏi Mornguard vì nhiều lý do khác nhau, và kinh nghiệm chiến đấu cũng như khả năng của họ không thể so sánh với những Lưu Đày thông thường.</t>
+          <t>Thủ Lĩnh Lưu Đày hầu hết đều là Resonator. Ví dụ như ở khu vực Huanglong, họ thường là những người bị trục xuất khỏi Mornguard vì nhiều lý do khác nhau, và kinh nghiệm chiến đấu cũng như khả năng của họ không thể so sánh với dân Lưu Đày thông thường.</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Ấu trùng linh trưởng đặc hữu của Rừng Mờ. Nhiều báo cáo cho thấy chúng thường di chuyển cùng cá thể trưởng thành, có trí thông minh tương đối cao nhưng khả năng di chuyển và mức độ nguy hiểm thấp hơn cá thể trưởng thành.</t>
+          <t>Ấu trùng Primate đặc hữu của Dim Forest. Nhiều báo cáo quan sát cho thấy chúng thường di chuyển cùng cá thể trưởng thành, có trí thông minh tương đối cao nhưng kém linh hoạt và ít nguy hiểm hơn cá thể trưởng thành.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Cyrscorpion</t>
+          <t>Bọ Cạp Cyr</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Sinh Vật Đột Biến Loài Small, phân bố rộng, có nhiều phân loài ở nhiều khu vực khác nhau, chủ yếu xuất hiện trong hang động, hầm mỏ và những nơi tối, ẩm ướt trên thế giới, mức độ nguy hiểm thấp.</t>
+          <t>Sinh Vật Đột Biến nhỏ, phân bố rộng rãi, với nhiều phân loài được ghi nhận ở nhiều khu vực khác nhau, chủ yếu sống trong hang động, hầm mỏ và những nơi tối tăm, ẩm ướt trên thế giới, mức độ nguy hiểm thấp.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Cyrscorpion là một trong số ít Sinh Vật Đột Biến có chung tên thông thường và phân loại khoa học.</t>
+          <t>Cyrscorpion là một trong số ít Sinh Vật Đột Biến có tên thông thường và phân loại khoa học trùng nhau.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Sinh Vật Đột Biến độc nhất ở Rừng Mờ. Nhiều báo cáo cho thấy những Sinh Vật Đột Biến này có trí thông minh tương đối cao, khả năng phối hợp nhóm mạnh, có thể chiến đấu theo đội và khá nguy hiểm.</t>
+          <t>Sinh Vật Đột Biến độc nhất tại Rừng Mờ. Nhiều báo cáo quan sát cho thấy loài Sinh Vật Đột Biến này có trí thông minh tương đối cao, khả năng phối hợp nhóm mạnh mẽ, có thể chiến đấu theo bầy đàn và khá nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Sinh vật đột biến cỡ lớn sống tại Khu Rừng Huanglong, thường di chuyển theo nhóm nhỏ 3-5 cá thể, có khứu giác nhạy bén và mức độ nguy hiểm nhất định.</t>
+          <t>Sinh Vật Đột Biến Cỡ Lớn sinh sống trong Rừng Huanglong, thường di chuyển theo nhóm nhỏ 3-5 cá thể, có khứu giác nhạy bén và mức độ nguy hiểm nhất định.</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Tên khoa học ba phần "Ursus spelaeus sagispina", chủ yếu sinh sống tại Khu Rừng Huanglong. Sinh Vật Đột Biến này có thị lực kém và chủ yếu dựa vào thính giác để săn mồi.</t>
+          <t>Tên ba phần "Ursus spelaeus sagispina", chủ yếu sinh sống tại Rừng Huanglong. Sinh Vật Đột Biến này có thị lực kém và chủ yếu dựa vào thính giác để săn mồi.</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Discord đặc trưng của Rừng Mờ. Theo báo cáo và yêu cầu bảo hiểm, nó có ham muốn săn mồi và tấn công mạnh mẽ, được cho là nguy hiểm.</t>
+          <t>Tacet Discord đặc trưng của Rừng Mờ. Các báo cáo và yêu cầu bồi thường bảo hiểm cho thấy nó có ham muốn săn mồi và tấn công mạnh mẽ, được đánh giá là nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Fractsidus Executioner</t>
+          <t>Đao Phủ Fractsidus</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Thunder Squama</t>
+          <t>Vảy Sấm Sét</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Một Discord mạnh mẽ xuất hiện tại Tacet Field ở Desorock Highlands, có khả năng sử dụng sức mạnh của Electro.</t>
+          <t>Một Tacet Discord mạnh mẽ xuất hiện tại Tổ Tacet của Desorock Highlands và có khả năng sử dụng sức mạnh của Electro.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Một Discord mạnh mẽ nằm tại Forsaken Abundance. Theo lời kể của nhân chứng, chuyển động của nó khác biệt so với các TD khác, cần nghiên cứu thêm để có thêm thông tin.</t>
+          <t>Một Tacet Discord mạnh mẽ xuất hiện tại Forsaken Abundance. Theo lời nhân chứng, chuyển động của nó khác biệt so với các TD khác, cần nghiên cứu thêm để có thông tin chi tiết.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Gleamtender</t>
+          <t>Ánh Sáng Dịu Dàng</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Discord mạnh mẽ sống trong các hầm sâu của Tiger's Maw. Rất ít báo cáo quan sát, tất cả đều cho rằng chúng giống côn trùng.</t>
+          <t>Tacet Discord mạnh mẽ trú ngụ trong những hầm sâu của Tiger's Maw. Rất ít báo cáo quan sát được ghi nhận, tất cả đều cho rằng chúng giống côn trùng.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Một Sinh Vật Đột Biến đáng gờm nằm sâu trong Rừng Mờ. Thủ lĩnh của bọn Hoochief.</t>
+          <t>Một Sinh Vật Đột Biến đáng gờm sâu trong Rừng Mờ. Thủ lĩnh của tộc Hoochief.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Một Discord đáng gờm làm tổ tại Whining Aix's Mire, tiếng gào thét của nó được người dân Huanglong gọi là "Khúc bi ca bất tận".</t>
+          <t>Một Tacet Discord đáng gờm trú ngụ tại Whining Aix's Mire, tiếng gào thét của nó được người dân Huanglong gọi là "Khúc bi ca bất tận".</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Một Discord được quan sát thấy ở Central Plains, chỉ có một báo cáo nhìn thấy TD này từ Rover. Không có ghi chép chi tiết về diện mạo đầy đủ của nó, và nó được đánh giá là cực kỳ nguy hiểm dựa trên mức năng lượng.</t>
+          <t>Một Tacet Discord được quan sát tại Central Plains, chỉ có duy nhất một báo cáo nhìn thấy từ Rover. Không có ghi chép chi tiết về hình dáng đầy đủ của nó, nhưng dựa trên mức năng lượng, nó được đánh giá là cực kỳ nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Sinh Vật Đột Biến cỡ lớn ẩn sâu trong Gorges of Spirit, được đánh giá là cực kỳ nguy hiểm. Chưa có ghi chép chi tiết về toàn bộ hình dạng của nó.</t>
+          <t>Sinh Vật Đột Biến Cỡ Lớn ẩn sâu trong Hẻm núi Spirit, được đánh giá là cực kỳ nguy hiểm. Chưa có ghi chép chi tiết về toàn bộ hình dạng của nó.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Một Sinh Vật Đột Biến có mức độ rủi ro thấp với hoạt động kỳ lạ, thường xuất hiện ở vùng nước của Whining Aix's Mire.</t>
+          <t>Một Sinh Vật Đột Biến có mức độ nguy hiểm thấp với kiểu hoạt động kỳ lạ, thường thấy ở vùng nước thuộc Whining Aix's Mire.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Trạm Tiến Triển</t>
+          <t>Căn Cứ Đang Phát Triển</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Trường Tacet Medium - Bộ Truyền Tín</t>
+          <t>Tổ Tacet Cỡ Trung - Bộ Truyền Tín</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Medium Tacet Field - Vũ khí</t>
+          <t>Tổ Tacet Cỡ Trung - Vũ Khí</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Vùng Tacet Medium - Echo</t>
+          <t>Tổ Tacet Cấp Trung - Echo</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Medium Tacet Field - Tacetite</t>
+          <t>Tổ Tacet Cấp Trung - Tacetite</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Thunder Squama</t>
+          <t>Vảy Sấm Sét</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Một Discord mạnh mẽ xuất hiện tại Tacet Field ở Desorock Highlands, có khả năng sử dụng sức mạnh của Electro.</t>
+          <t>Một Tacet Discord mạnh mẽ xuất hiện tại Tổ Tacet của Desorock Highlands và có khả năng sử dụng sức mạnh của Electro.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Vảy Sấm có hình dạng giống sự kết hợp giữa người và thằn lằn. Nó có thể sử dụng Wutheron trong Tacet Field để thực hiện các thao tác cơ động tốc độ cao. Ban đầu, nó được đánh giá là kết quả của quá trình tiến hóa tự nhiên của TD.</t>
+          <t>Thunder Squama có hình dạng giống sự kết hợp giữa người và thằn lằn. Nó có thể sử dụng Wutheron trong Tổ Tacet để thực hiện các động tác cơ động tốc độ cao. Ban đầu, nó được cho là kết quả của quá trình tiến hóa tự nhiên của TD.</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Một Discord được quan sát thấy ở Central Plains, chỉ có một báo cáo nhìn thấy TD này từ Rover. Không có ghi chép chi tiết về diện mạo đầy đủ của nó, và nó được đánh giá là cực kỳ nguy hiểm dựa trên mức năng lượng.</t>
+          <t>Một Tacet Discord được quan sát tại Central Plains, chỉ có duy nhất một báo cáo nhìn thấy từ Rover. Không có ghi chép chi tiết về hình dáng đầy đủ của nó, nhưng dựa trên mức năng lượng, nó được đánh giá là cực kỳ nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Bản sao của "Vô Vương" Threnody. Vẻ ngoài giống một hiệp sĩ mặc giáp trắng, khi sức mạnh tăng lên, nó sẽ xòe đôi cánh đỏ như máu, có lẽ do tạm thời điều khiển cấu trúc Wutheron trong cơ thể, giúp tăng khả năng di chuyển và sức tấn công tức thì. Gần đây, người ta còn phát hiện nó có thể tạo ra cấu trúc cơ thể mô phỏng "vũ khí" của con người.</t>
+          <t>Bản sao của "Crownless" thuộc Threnody. Về ngoại hình, nó giống một hiệp sĩ mặc giáp trắng, và khi sức mạnh tăng lên, đôi cánh đỏ như máu sẽ bung ra, có lẽ do nó tạm thời điều khiển cấu trúc Wutheron trong cơ thể, giúp tăng khả năng di chuyển và sức tấn công tức thì. Gần đây, người ta còn quan sát thấy nó có thể tạo ra cấu trúc cơ thể mô phỏng "vũ khí" của con người.</t>
         </is>
       </c>
     </row>
